--- a/data/trans_dic/P23_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P23_R-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,32; 39,14</t>
+          <t>33,3; 39,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,24; 37,66</t>
+          <t>31,39; 37,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,72; 33,33</t>
+          <t>26,52; 33,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,61; 15,39</t>
+          <t>11,5; 15,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,05; 16,98</t>
+          <t>13,05; 16,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,76; 16,0</t>
+          <t>11,51; 16,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,84; 25,5</t>
+          <t>21,78; 25,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,38; 24,95</t>
+          <t>21,45; 24,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,78; 22,56</t>
+          <t>18,6; 22,64</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,85; 50,6</t>
+          <t>45,85; 50,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,26; 45,9</t>
+          <t>41,23; 45,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,18; 41,49</t>
+          <t>37,02; 41,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,29; 37,0</t>
+          <t>32,24; 36,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,96; 38,41</t>
+          <t>33,85; 38,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,3; 35,29</t>
+          <t>31,22; 35,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,96; 43,33</t>
+          <t>40,05; 43,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,36; 41,74</t>
+          <t>38,49; 41,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,95; 37,82</t>
+          <t>34,86; 37,98</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,12; 39,13</t>
+          <t>31,22; 39,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,41; 38,53</t>
+          <t>29,58; 38,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,83; 29,7</t>
+          <t>21,76; 29,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,79; 33,62</t>
+          <t>24,92; 33,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,2; 35,24</t>
+          <t>26,08; 35,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,37; 25,72</t>
+          <t>18,92; 25,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,69; 35,43</t>
+          <t>29,05; 35,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,65; 35,19</t>
+          <t>28,57; 35,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,36; 26,85</t>
+          <t>21,32; 26,73</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,46; 44,04</t>
+          <t>40,59; 44,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,67; 41,21</t>
+          <t>37,81; 41,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,27; 36,45</t>
+          <t>33,32; 36,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,11; 27,19</t>
+          <t>24,15; 26,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,92; 28,98</t>
+          <t>25,96; 28,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,63; 27,65</t>
+          <t>24,54; 27,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,61; 34,98</t>
+          <t>32,56; 35,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,25; 34,72</t>
+          <t>32,22; 34,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,38; 31,5</t>
+          <t>29,21; 31,52</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>343415; 403370</t>
+          <t>343258; 403903</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>304493; 367080</t>
+          <t>305920; 364630</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>201325; 251110</t>
+          <t>199850; 248706</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152741; 202332</t>
+          <t>151270; 201274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>174531; 227111</t>
+          <t>174524; 226179</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>116721; 158762</t>
+          <t>114211; 159950</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>512316; 598216</t>
+          <t>511026; 592873</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>494288; 576840</t>
+          <t>496028; 575016</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>327859; 393831</t>
+          <t>324724; 395155</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>776435; 856802</t>
+          <t>776392; 860662</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>809829; 901014</t>
+          <t>809383; 899273</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>771960; 861452</t>
+          <t>768647; 862257</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>512636; 587509</t>
+          <t>511913; 586028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>596326; 674362</t>
+          <t>594334; 681069</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>621697; 700932</t>
+          <t>620156; 701912</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1310990; 1421728</t>
+          <t>1314119; 1422658</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1426527; 1552200</t>
+          <t>1431162; 1554068</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1419959; 1536556</t>
+          <t>1416366; 1542879</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>171606; 215756</t>
+          <t>172156; 218160</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>141496; 185384</t>
+          <t>142337; 186266</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119147; 162089</t>
+          <t>118753; 162069</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118092; 160162</t>
+          <t>118718; 157472</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>120165; 161618</t>
+          <t>119601; 160980</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>100729; 140995</t>
+          <t>103734; 141885</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>305186; 364147</t>
+          <t>298590; 360368</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>269212; 330702</t>
+          <t>268541; 330776</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>233695; 293782</t>
+          <t>233292; 292393</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1325414; 1442511</t>
+          <t>1329366; 1446641</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1287856; 1408934</t>
+          <t>1292537; 1410444</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1123252; 1230497</t>
+          <t>1124670; 1236113</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>814610; 918767</t>
+          <t>815961; 910974</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>920751; 1029355</t>
+          <t>922325; 1029308</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>868743; 974982</t>
+          <t>865306; 972186</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2170312; 2328069</t>
+          <t>2166858; 2330261</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2248048; 2420260</t>
+          <t>2245923; 2410285</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2027632; 2174506</t>
+          <t>2015941; 2175298</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P23_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P23_R-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,3; 39,19</t>
+          <t>33,29; 39,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,39; 37,41</t>
+          <t>31,14; 37,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,52; 33,01</t>
+          <t>26,94; 33,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,5; 15,3</t>
+          <t>11,63; 15,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,05; 16,91</t>
+          <t>13,07; 16,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,51; 16,12</t>
+          <t>11,77; 16,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,78; 25,27</t>
+          <t>21,76; 25,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,45; 24,87</t>
+          <t>21,31; 24,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,6; 22,64</t>
+          <t>18,91; 22,75</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,85; 50,82</t>
+          <t>45,93; 50,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,23; 45,81</t>
+          <t>41,38; 45,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,02; 41,53</t>
+          <t>37,0; 41,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,24; 36,91</t>
+          <t>32,37; 36,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,85; 38,79</t>
+          <t>34,11; 38,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,22; 35,34</t>
+          <t>31,25; 35,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,05; 43,36</t>
+          <t>39,76; 43,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,49; 41,79</t>
+          <t>38,42; 41,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,86; 37,98</t>
+          <t>34,9; 37,82</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,22; 39,56</t>
+          <t>31,05; 39,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,58; 38,71</t>
+          <t>29,55; 38,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,76; 29,69</t>
+          <t>21,79; 29,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,92; 33,05</t>
+          <t>25,36; 33,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,08; 35,1</t>
+          <t>25,95; 35,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,92; 25,88</t>
+          <t>19,04; 26,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,05; 35,06</t>
+          <t>29,4; 34,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,57; 35,2</t>
+          <t>28,85; 35,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,32; 26,73</t>
+          <t>21,33; 26,43</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,59; 44,17</t>
+          <t>40,64; 44,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,81; 41,26</t>
+          <t>37,77; 41,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,32; 36,62</t>
+          <t>33,15; 36,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,15; 26,96</t>
+          <t>24,13; 27,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,96; 28,98</t>
+          <t>25,95; 29,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,54; 27,57</t>
+          <t>24,43; 27,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,56; 35,02</t>
+          <t>32,66; 34,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,22; 34,58</t>
+          <t>32,21; 34,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,21; 31,52</t>
+          <t>29,39; 31,52</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>343258; 403903</t>
+          <t>343070; 407942</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>305920; 364630</t>
+          <t>303467; 364886</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199850; 248706</t>
+          <t>202974; 254062</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>151270; 201274</t>
+          <t>152886; 203466</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>174524; 226179</t>
+          <t>174847; 227068</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>114211; 159950</t>
+          <t>116831; 160636</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>511026; 592873</t>
+          <t>510377; 592930</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>496028; 575016</t>
+          <t>492818; 574832</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>324724; 395155</t>
+          <t>330072; 397174</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>776392; 860662</t>
+          <t>777751; 853855</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>809383; 899273</t>
+          <t>812238; 899519</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>768647; 862257</t>
+          <t>768343; 859360</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>511913; 586028</t>
+          <t>513991; 584449</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>594334; 681069</t>
+          <t>598914; 676508</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>620156; 701912</t>
+          <t>620750; 703139</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1314119; 1422658</t>
+          <t>1304468; 1419599</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1431162; 1554068</t>
+          <t>1428581; 1555373</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1416366; 1542879</t>
+          <t>1417667; 1536575</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>172156; 218160</t>
+          <t>171191; 215947</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>142337; 186266</t>
+          <t>142206; 183992</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>118753; 162069</t>
+          <t>118932; 161596</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118718; 157472</t>
+          <t>120836; 160485</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>119601; 160980</t>
+          <t>118996; 161780</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>103734; 141885</t>
+          <t>104369; 143522</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>298590; 360368</t>
+          <t>302193; 357854</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>268541; 330776</t>
+          <t>271135; 330740</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>233292; 292393</t>
+          <t>233363; 289182</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1329366; 1446641</t>
+          <t>1331274; 1442553</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1292537; 1410444</t>
+          <t>1291250; 1409139</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1124670; 1236113</t>
+          <t>1118997; 1234423</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>815961; 910974</t>
+          <t>815438; 919173</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>922325; 1029308</t>
+          <t>921679; 1032651</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>865306; 972186</t>
+          <t>861684; 975279</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2166858; 2330261</t>
+          <t>2173732; 2325182</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2245923; 2410285</t>
+          <t>2245598; 2410048</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2015941; 2175298</t>
+          <t>2028494; 2175877</t>
         </is>
       </c>
     </row>
